--- a/www/flightdata/xlsx/eoss-345.xlsx
+++ b/www/flightdata/xlsx/eoss-345.xlsx
@@ -3171,7 +3171,7 @@
         <v>31116.12</v>
       </c>
       <c r="I2">
-        <v>531</v>
+        <v>392</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
